--- a/data/meteo/modele.xlsx
+++ b/data/meteo/modele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adfayad\Desktop\PSE\Simulateur_chaineEtg\data\meteo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A90D423E-C2DC-47CD-81C6-F3FF3C35A53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B343CE51-CCE2-42A5-AABB-A78D3A75B902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E8ED991B-B712-4621-955E-BA0B6DF88A1F}"/>
   </bookViews>
@@ -271,7 +271,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,16 +279,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -296,15 +333,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,268 +713,271 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="68.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>23</v>
       </c>
     </row>
